--- a/pages/WR_progressions/Medals_Men_TS.xlsx
+++ b/pages/WR_progressions/Medals_Men_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9794F85E-1A4E-4BD1-B6A5-A03FC5F6328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664C088-B95B-40DE-962A-B7683EC39954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
@@ -36,18 +36,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
   <si>
-    <t>Gold_Time</t>
+    <t>Competition</t>
   </si>
   <si>
-    <t>Bronze_Time</t>
+    <t>OLY</t>
   </si>
   <si>
-    <t>Silver_Time</t>
+    <t>WCH</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>8th</t>
   </si>
 </sst>
 </file>
@@ -83,9 +95,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,110 +431,573 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.73046875" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>42.045999999999999</v>
+      </c>
+      <c r="D2">
+        <v>42.530999999999999</v>
+      </c>
+      <c r="E2">
+        <v>42.915999999999997</v>
+      </c>
+      <c r="F2">
+        <v>43.658000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>41.896000000000001</v>
+      </c>
+      <c r="D3">
+        <v>41.993000000000002</v>
+      </c>
+      <c r="E3">
+        <v>42.851999999999997</v>
+      </c>
+      <c r="F3">
+        <v>43.707000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>42.69</v>
+      </c>
+      <c r="D4">
+        <v>42.965000000000003</v>
+      </c>
+      <c r="E4">
+        <v>43.250999999999998</v>
+      </c>
+      <c r="F4">
+        <v>44.414000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="1">
-        <v>42.331000000000003</v>
-      </c>
-      <c r="C2" s="1">
-        <v>41.829000000000001</v>
-      </c>
-      <c r="D2" s="1">
-        <v>41.369</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="C5">
+        <v>42.134</v>
+      </c>
+      <c r="D5">
+        <v>42.231000000000002</v>
+      </c>
+      <c r="E5">
+        <v>42.371000000000002</v>
+      </c>
+      <c r="F5">
+        <v>43.515999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2020</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>41.987000000000002</v>
+      </c>
+      <c r="D6">
+        <v>42.470999999999997</v>
+      </c>
+      <c r="E6">
+        <v>42.805</v>
+      </c>
+      <c r="F6">
+        <v>43.235999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>2019</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>42.573999999999998</v>
+      </c>
+      <c r="D7">
+        <v>43.357999999999997</v>
+      </c>
+      <c r="E7">
+        <v>43.387999999999998</v>
+      </c>
+      <c r="F7">
+        <v>43.704000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2018</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>42.869</v>
+      </c>
+      <c r="D8">
+        <v>43.389000000000003</v>
+      </c>
+      <c r="E8">
+        <v>43.451999999999998</v>
+      </c>
+      <c r="F8">
+        <v>44.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>43.267000000000003</v>
+      </c>
+      <c r="D9">
+        <v>43.39</v>
+      </c>
+      <c r="E9">
+        <v>43.415999999999997</v>
+      </c>
+      <c r="F9">
+        <v>44.363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2016</v>
       </c>
-      <c r="B3" s="1">
-        <v>43.143000000000001</v>
-      </c>
-      <c r="C3" s="1">
-        <v>42.542000000000002</v>
-      </c>
-      <c r="D3" s="1">
-        <v>42.44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4">
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>42.561999999999998</v>
+      </c>
+      <c r="D10">
+        <v>42.673000000000002</v>
+      </c>
+      <c r="E10">
+        <v>43.158000000000001</v>
+      </c>
+      <c r="F10">
+        <v>44.262999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2016</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>43.095999999999997</v>
+      </c>
+      <c r="D11">
+        <v>43.265999999999998</v>
+      </c>
+      <c r="E11">
+        <v>43.487000000000002</v>
+      </c>
+      <c r="F11">
+        <v>43.750999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>2015</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>42.892000000000003</v>
+      </c>
+      <c r="D12">
+        <v>43.072000000000003</v>
+      </c>
+      <c r="E12">
+        <v>43.136000000000003</v>
+      </c>
+      <c r="F12">
+        <v>43.808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>2014</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>43.064999999999998</v>
+      </c>
+      <c r="D13">
+        <v>43.301000000000002</v>
+      </c>
+      <c r="E13">
+        <v>43.454000000000001</v>
+      </c>
+      <c r="F13">
+        <v>43.924999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>43.58</v>
+      </c>
+      <c r="D14">
+        <v>43.731000000000002</v>
+      </c>
+      <c r="E14">
+        <v>43.792000000000002</v>
+      </c>
+      <c r="F14">
+        <v>44.854999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>2012</v>
       </c>
-      <c r="B4" s="1">
-        <v>43.209000000000003</v>
-      </c>
-      <c r="C4" s="1">
-        <v>43.012999999999998</v>
-      </c>
-      <c r="D4" s="1">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>43.247</v>
+      </c>
+      <c r="D15">
+        <v>43.512</v>
+      </c>
+      <c r="E15">
+        <v>43.741999999999997</v>
+      </c>
+      <c r="F15">
+        <v>44.399000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>2012</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>43.064999999999998</v>
+      </c>
+      <c r="D16">
+        <v>43.097000000000001</v>
+      </c>
+      <c r="E16">
+        <v>43.377000000000002</v>
+      </c>
+      <c r="F16">
+        <v>44.323999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>2011</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>43.951000000000001</v>
+      </c>
+      <c r="D17">
+        <v>44.100999999999999</v>
+      </c>
+      <c r="E17">
+        <v>44.128</v>
+      </c>
+      <c r="F17">
+        <v>45.112000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>2010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>43.372999999999998</v>
+      </c>
+      <c r="D18">
+        <v>43.457999999999998</v>
+      </c>
+      <c r="E18">
+        <v>43.802</v>
+      </c>
+      <c r="F18">
+        <v>44.63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2009</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>43.613999999999997</v>
+      </c>
+      <c r="D19">
+        <v>43.738</v>
+      </c>
+      <c r="E19">
+        <v>43.911000000000001</v>
+      </c>
+      <c r="F19">
+        <v>45.139000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20">
         <v>2008</v>
       </c>
-      <c r="B5" s="1">
-        <v>44.014000000000003</v>
-      </c>
-      <c r="C5" s="1">
-        <v>43.651000000000003</v>
-      </c>
-      <c r="D5" s="1">
-        <v>43.128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>42.95</v>
+      </c>
+      <c r="D20">
+        <v>43.540999999999997</v>
+      </c>
+      <c r="E20">
+        <v>44.197000000000003</v>
+      </c>
+      <c r="F20">
+        <v>45.345999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>2008</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>43.514000000000003</v>
+      </c>
+      <c r="D21">
+        <v>43.91</v>
+      </c>
+      <c r="E21">
+        <v>43.957999999999998</v>
+      </c>
+      <c r="F21">
+        <v>45.030999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>2007</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>43.917000000000002</v>
+      </c>
+      <c r="D22">
+        <v>44.036000000000001</v>
+      </c>
+      <c r="E22">
+        <v>44.137999999999998</v>
+      </c>
+      <c r="F22">
+        <v>45.487000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>2006</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>44.194000000000003</v>
+      </c>
+      <c r="D23">
+        <v>44.406999999999996</v>
+      </c>
+      <c r="E23">
+        <v>44.591000000000001</v>
+      </c>
+      <c r="F23">
+        <v>45.707999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>2005</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>44.337000000000003</v>
+      </c>
+      <c r="D24">
+        <v>44.575000000000003</v>
+      </c>
+      <c r="E24">
+        <v>44.631999999999998</v>
+      </c>
+      <c r="F24">
+        <v>46.597000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25">
         <v>2004</v>
       </c>
-      <c r="B6" s="1">
-        <v>44.359000000000002</v>
-      </c>
-      <c r="C6" s="1">
-        <v>44.246000000000002</v>
-      </c>
-      <c r="D6" s="1">
-        <v>43.98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>44.421999999999997</v>
+      </c>
+      <c r="D25">
+        <v>44.481999999999999</v>
+      </c>
+      <c r="E25">
+        <v>44.844999999999999</v>
+      </c>
+      <c r="F25">
+        <v>45.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>2004</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>44.179000000000002</v>
+      </c>
+      <c r="D26">
+        <v>44.250999999999998</v>
+      </c>
+      <c r="E26">
+        <v>44.354999999999997</v>
+      </c>
+      <c r="F26">
+        <v>44.985999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>2002</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>44.813000000000002</v>
+      </c>
+      <c r="D27">
+        <v>44.890999999999998</v>
+      </c>
+      <c r="E27">
+        <v>44.957999999999998</v>
+      </c>
+      <c r="F27">
+        <v>45.982999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28">
         <v>2000</v>
       </c>
-      <c r="B7" s="1">
-        <v>45.161000000000001</v>
-      </c>
-      <c r="C7" s="1">
-        <v>44.68</v>
-      </c>
-      <c r="D7" s="1">
-        <v>44.232999999999997</v>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>44.424999999999997</v>
+      </c>
+      <c r="D28">
+        <v>44.658999999999999</v>
+      </c>
+      <c r="E28">
+        <v>44.719000000000001</v>
+      </c>
+      <c r="F28">
+        <v>45.701000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/pages/WR_progressions/Medals_Men_TS.xlsx
+++ b/pages/WR_progressions/Medals_Men_TS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664C088-B95B-40DE-962A-B7683EC39954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F1EA8-CB89-42E4-A1CB-7B505E6E13B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="3218" yWindow="1440" windowWidth="14400" windowHeight="8190" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -95,8 +95,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -440,7 +443,7 @@
     <col min="5" max="5" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,384 +463,387 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>41.279000000000003</v>
+      </c>
+      <c r="D2" s="1">
+        <v>41.862000000000002</v>
+      </c>
+      <c r="E2" s="1">
+        <v>42.072000000000003</v>
+      </c>
+      <c r="F2" s="1">
+        <v>43.905000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3">
         <v>2023</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
         <v>42.045999999999999</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>42.530999999999999</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>42.915999999999997</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>43.658000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4">
         <v>2022</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>41.896000000000001</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>41.993000000000002</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>42.851999999999997</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>43.707000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>2021</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>42.69</v>
-      </c>
-      <c r="D4">
-        <v>42.965000000000003</v>
-      </c>
-      <c r="E4">
-        <v>43.250999999999998</v>
-      </c>
-      <c r="F4">
-        <v>44.414000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2021</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>42.69</v>
+      </c>
+      <c r="D5">
+        <v>42.965000000000003</v>
+      </c>
+      <c r="E5">
+        <v>43.250999999999998</v>
+      </c>
+      <c r="F5">
+        <v>44.414000000000001</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>42.134</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>42.231000000000002</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>42.371000000000002</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>43.515999999999998</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7">
         <v>2020</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
         <v>41.987000000000002</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>42.470999999999997</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>42.805</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>43.235999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8">
         <v>2019</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
         <v>42.573999999999998</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>43.357999999999997</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>43.387999999999998</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>43.704000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9">
         <v>2018</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
         <v>42.869</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>43.389000000000003</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>43.451999999999998</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>44.41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2017</v>
       </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
         <v>43.267000000000003</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>43.39</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>43.415999999999997</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>44.363</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>2016</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>42.561999999999998</v>
-      </c>
-      <c r="D10">
-        <v>42.673000000000002</v>
-      </c>
-      <c r="E10">
-        <v>43.158000000000001</v>
-      </c>
-      <c r="F10">
-        <v>44.262999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2016</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
+        <v>42.561999999999998</v>
+      </c>
+      <c r="D11">
+        <v>42.673000000000002</v>
+      </c>
+      <c r="E11">
+        <v>43.158000000000001</v>
+      </c>
+      <c r="F11">
+        <v>44.262999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>2016</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>43.095999999999997</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>43.265999999999998</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>43.487000000000002</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>43.750999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13">
         <v>2015</v>
       </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12">
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
         <v>42.892000000000003</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>43.072000000000003</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>43.136000000000003</v>
       </c>
-      <c r="F12">
+      <c r="F13">
         <v>43.808</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14">
         <v>2014</v>
       </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
         <v>43.064999999999998</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>43.301000000000002</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>43.454000000000001</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>43.924999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>2013</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
         <v>43.58</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>43.731000000000002</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>43.792000000000002</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>2012</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>43.247</v>
-      </c>
-      <c r="D15">
-        <v>43.512</v>
-      </c>
-      <c r="E15">
-        <v>43.741999999999997</v>
-      </c>
-      <c r="F15">
-        <v>44.399000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2012</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>43.064999999999998</v>
+        <v>43.247</v>
       </c>
       <c r="D16">
-        <v>43.097000000000001</v>
+        <v>43.512</v>
       </c>
       <c r="E16">
-        <v>43.377000000000002</v>
+        <v>43.741999999999997</v>
       </c>
       <c r="F16">
-        <v>44.323999999999998</v>
+        <v>44.399000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>43.951000000000001</v>
+        <v>43.064999999999998</v>
       </c>
       <c r="D17">
-        <v>44.100999999999999</v>
+        <v>43.097000000000001</v>
       </c>
       <c r="E17">
-        <v>44.128</v>
+        <v>43.377000000000002</v>
       </c>
       <c r="F17">
-        <v>45.112000000000002</v>
+        <v>44.323999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>43.372999999999998</v>
+        <v>43.951000000000001</v>
       </c>
       <c r="D18">
-        <v>43.457999999999998</v>
+        <v>44.100999999999999</v>
       </c>
       <c r="E18">
-        <v>43.802</v>
+        <v>44.128</v>
       </c>
       <c r="F18">
-        <v>44.63</v>
+        <v>45.112000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>43.613999999999997</v>
+        <v>43.372999999999998</v>
       </c>
       <c r="D19">
-        <v>43.738</v>
+        <v>43.457999999999998</v>
       </c>
       <c r="E19">
-        <v>43.911000000000001</v>
+        <v>43.802</v>
       </c>
       <c r="F19">
-        <v>45.139000000000003</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>42.95</v>
+        <v>43.613999999999997</v>
       </c>
       <c r="D20">
-        <v>43.540999999999997</v>
+        <v>43.738</v>
       </c>
       <c r="E20">
-        <v>44.197000000000003</v>
+        <v>43.911000000000001</v>
       </c>
       <c r="F20">
-        <v>45.345999999999997</v>
+        <v>45.139000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
@@ -845,99 +851,99 @@
         <v>2008</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>43.514000000000003</v>
+        <v>42.95</v>
       </c>
       <c r="D21">
-        <v>43.91</v>
+        <v>43.540999999999997</v>
       </c>
       <c r="E21">
-        <v>43.957999999999998</v>
+        <v>44.197000000000003</v>
       </c>
       <c r="F21">
-        <v>45.030999999999999</v>
+        <v>45.345999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
       <c r="C22">
-        <v>43.917000000000002</v>
+        <v>43.514000000000003</v>
       </c>
       <c r="D22">
-        <v>44.036000000000001</v>
+        <v>43.91</v>
       </c>
       <c r="E22">
-        <v>44.137999999999998</v>
+        <v>43.957999999999998</v>
       </c>
       <c r="F22">
-        <v>45.487000000000002</v>
+        <v>45.030999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23">
-        <v>44.194000000000003</v>
+        <v>43.917000000000002</v>
       </c>
       <c r="D23">
-        <v>44.406999999999996</v>
+        <v>44.036000000000001</v>
       </c>
       <c r="E23">
-        <v>44.591000000000001</v>
+        <v>44.137999999999998</v>
       </c>
       <c r="F23">
-        <v>45.707999999999998</v>
+        <v>45.487000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>44.337000000000003</v>
+        <v>44.194000000000003</v>
       </c>
       <c r="D24">
-        <v>44.575000000000003</v>
+        <v>44.406999999999996</v>
       </c>
       <c r="E24">
-        <v>44.631999999999998</v>
+        <v>44.591000000000001</v>
       </c>
       <c r="F24">
-        <v>46.597000000000001</v>
+        <v>45.707999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
       </c>
       <c r="C25">
-        <v>44.421999999999997</v>
+        <v>44.337000000000003</v>
       </c>
       <c r="D25">
-        <v>44.481999999999999</v>
+        <v>44.575000000000003</v>
       </c>
       <c r="E25">
-        <v>44.844999999999999</v>
+        <v>44.631999999999998</v>
       </c>
       <c r="F25">
-        <v>45.31</v>
+        <v>46.597000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
@@ -945,58 +951,78 @@
         <v>2004</v>
       </c>
       <c r="B26" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>44.179000000000002</v>
+        <v>44.421999999999997</v>
       </c>
       <c r="D26">
-        <v>44.250999999999998</v>
+        <v>44.481999999999999</v>
       </c>
       <c r="E26">
-        <v>44.354999999999997</v>
+        <v>44.844999999999999</v>
       </c>
       <c r="F26">
-        <v>44.985999999999997</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>44.813000000000002</v>
+        <v>44.179000000000002</v>
       </c>
       <c r="D27">
-        <v>44.890999999999998</v>
+        <v>44.250999999999998</v>
       </c>
       <c r="E27">
-        <v>44.957999999999998</v>
+        <v>44.354999999999997</v>
       </c>
       <c r="F27">
-        <v>45.982999999999997</v>
+        <v>44.985999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28">
+        <v>2002</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>44.813000000000002</v>
+      </c>
+      <c r="D28">
+        <v>44.890999999999998</v>
+      </c>
+      <c r="E28">
+        <v>44.957999999999998</v>
+      </c>
+      <c r="F28">
+        <v>45.982999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29">
         <v>2000</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>2</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>44.424999999999997</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <v>44.658999999999999</v>
       </c>
-      <c r="E28">
+      <c r="E29">
         <v>44.719000000000001</v>
       </c>
-      <c r="F28">
+      <c r="F29">
         <v>45.701000000000001</v>
       </c>
     </row>

--- a/pages/WR_progressions/Medals_Men_TS.xlsx
+++ b/pages/WR_progressions/Medals_Men_TS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F1EA8-CB89-42E4-A1CB-7B505E6E13B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E039E70-9AE9-45E1-B1A4-0B703C96B76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3218" yWindow="1440" windowWidth="14400" windowHeight="8190" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -468,80 +468,79 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>41.279000000000003</v>
-      </c>
-      <c r="D2" s="1">
-        <v>41.862000000000002</v>
-      </c>
-      <c r="E2" s="1">
-        <v>42.072000000000003</v>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>42.588999999999999</v>
+      </c>
+      <c r="D2">
+        <v>42.993000000000002</v>
+      </c>
+      <c r="E2">
+        <v>42.997999999999998</v>
       </c>
       <c r="F2" s="1">
-        <v>43.905000000000001</v>
+        <v>44.186</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>42.045999999999999</v>
-      </c>
-      <c r="D3">
-        <v>42.530999999999999</v>
-      </c>
-      <c r="E3">
-        <v>42.915999999999997</v>
-      </c>
-      <c r="F3">
-        <v>43.658000000000001</v>
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>41.279000000000003</v>
+      </c>
+      <c r="D3" s="1">
+        <v>41.862000000000002</v>
+      </c>
+      <c r="E3" s="1">
+        <v>42.072000000000003</v>
+      </c>
+      <c r="F3" s="1">
+        <v>43.905000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>41.896000000000001</v>
+        <v>42.045999999999999</v>
       </c>
       <c r="D4">
-        <v>41.993000000000002</v>
+        <v>42.530999999999999</v>
       </c>
       <c r="E4">
-        <v>42.851999999999997</v>
+        <v>42.915999999999997</v>
       </c>
       <c r="F4">
-        <v>43.707000000000001</v>
-      </c>
-      <c r="H4" s="1"/>
+        <v>43.658000000000001</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>42.69</v>
+        <v>41.896000000000001</v>
       </c>
       <c r="D5">
-        <v>42.965000000000003</v>
+        <v>41.993000000000002</v>
       </c>
       <c r="E5">
-        <v>43.250999999999998</v>
+        <v>42.851999999999997</v>
       </c>
       <c r="F5">
-        <v>44.414000000000001</v>
+        <v>43.707000000000001</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -550,120 +549,121 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>42.134</v>
+        <v>42.69</v>
       </c>
       <c r="D6">
-        <v>42.231000000000002</v>
+        <v>42.965000000000003</v>
       </c>
       <c r="E6">
-        <v>42.371000000000002</v>
+        <v>43.250999999999998</v>
       </c>
       <c r="F6">
-        <v>43.515999999999998</v>
+        <v>44.414000000000001</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>41.987000000000002</v>
+        <v>42.134</v>
       </c>
       <c r="D7">
-        <v>42.470999999999997</v>
+        <v>42.231000000000002</v>
       </c>
       <c r="E7">
-        <v>42.805</v>
+        <v>42.371000000000002</v>
       </c>
       <c r="F7">
-        <v>43.235999999999997</v>
-      </c>
+        <v>43.515999999999998</v>
+      </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>42.573999999999998</v>
+        <v>41.987000000000002</v>
       </c>
       <c r="D8">
-        <v>43.357999999999997</v>
+        <v>42.470999999999997</v>
       </c>
       <c r="E8">
-        <v>43.387999999999998</v>
+        <v>42.805</v>
       </c>
       <c r="F8">
-        <v>43.704000000000001</v>
+        <v>43.235999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>42.869</v>
+        <v>42.573999999999998</v>
       </c>
       <c r="D9">
-        <v>43.389000000000003</v>
+        <v>43.357999999999997</v>
       </c>
       <c r="E9">
-        <v>43.451999999999998</v>
+        <v>43.387999999999998</v>
       </c>
       <c r="F9">
-        <v>44.41</v>
+        <v>43.704000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>43.267000000000003</v>
+        <v>42.869</v>
       </c>
       <c r="D10">
-        <v>43.39</v>
+        <v>43.389000000000003</v>
       </c>
       <c r="E10">
-        <v>43.415999999999997</v>
+        <v>43.451999999999998</v>
       </c>
       <c r="F10">
-        <v>44.363</v>
+        <v>44.41</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>42.561999999999998</v>
+        <v>43.267000000000003</v>
       </c>
       <c r="D11">
-        <v>42.673000000000002</v>
+        <v>43.39</v>
       </c>
       <c r="E11">
-        <v>43.158000000000001</v>
+        <v>43.415999999999997</v>
       </c>
       <c r="F11">
-        <v>44.262999999999998</v>
+        <v>44.363</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
@@ -671,99 +671,99 @@
         <v>2016</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>43.095999999999997</v>
+        <v>42.561999999999998</v>
       </c>
       <c r="D12">
-        <v>43.265999999999998</v>
+        <v>42.673000000000002</v>
       </c>
       <c r="E12">
-        <v>43.487000000000002</v>
+        <v>43.158000000000001</v>
       </c>
       <c r="F12">
-        <v>43.750999999999998</v>
+        <v>44.262999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
       </c>
       <c r="C13">
-        <v>42.892000000000003</v>
+        <v>43.095999999999997</v>
       </c>
       <c r="D13">
-        <v>43.072000000000003</v>
+        <v>43.265999999999998</v>
       </c>
       <c r="E13">
-        <v>43.136000000000003</v>
+        <v>43.487000000000002</v>
       </c>
       <c r="F13">
-        <v>43.808</v>
+        <v>43.750999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>43.064999999999998</v>
+        <v>42.892000000000003</v>
       </c>
       <c r="D14">
-        <v>43.301000000000002</v>
+        <v>43.072000000000003</v>
       </c>
       <c r="E14">
-        <v>43.454000000000001</v>
+        <v>43.136000000000003</v>
       </c>
       <c r="F14">
-        <v>43.924999999999997</v>
+        <v>43.808</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>43.58</v>
+        <v>43.064999999999998</v>
       </c>
       <c r="D15">
-        <v>43.731000000000002</v>
+        <v>43.301000000000002</v>
       </c>
       <c r="E15">
-        <v>43.792000000000002</v>
+        <v>43.454000000000001</v>
       </c>
       <c r="F15">
-        <v>44.854999999999997</v>
+        <v>43.924999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>43.247</v>
+        <v>43.58</v>
       </c>
       <c r="D16">
-        <v>43.512</v>
+        <v>43.731000000000002</v>
       </c>
       <c r="E16">
-        <v>43.741999999999997</v>
+        <v>43.792000000000002</v>
       </c>
       <c r="F16">
-        <v>44.399000000000001</v>
+        <v>44.854999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
@@ -771,99 +771,99 @@
         <v>2012</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>43.064999999999998</v>
+        <v>43.247</v>
       </c>
       <c r="D17">
-        <v>43.097000000000001</v>
+        <v>43.512</v>
       </c>
       <c r="E17">
-        <v>43.377000000000002</v>
+        <v>43.741999999999997</v>
       </c>
       <c r="F17">
-        <v>44.323999999999998</v>
+        <v>44.399000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>43.951000000000001</v>
+        <v>43.064999999999998</v>
       </c>
       <c r="D18">
-        <v>44.100999999999999</v>
+        <v>43.097000000000001</v>
       </c>
       <c r="E18">
-        <v>44.128</v>
+        <v>43.377000000000002</v>
       </c>
       <c r="F18">
-        <v>45.112000000000002</v>
+        <v>44.323999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>43.372999999999998</v>
+        <v>43.951000000000001</v>
       </c>
       <c r="D19">
-        <v>43.457999999999998</v>
+        <v>44.100999999999999</v>
       </c>
       <c r="E19">
-        <v>43.802</v>
+        <v>44.128</v>
       </c>
       <c r="F19">
-        <v>44.63</v>
+        <v>45.112000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>43.613999999999997</v>
+        <v>43.372999999999998</v>
       </c>
       <c r="D20">
-        <v>43.738</v>
+        <v>43.457999999999998</v>
       </c>
       <c r="E20">
-        <v>43.911000000000001</v>
+        <v>43.802</v>
       </c>
       <c r="F20">
-        <v>45.139000000000003</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B21" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>42.95</v>
+        <v>43.613999999999997</v>
       </c>
       <c r="D21">
-        <v>43.540999999999997</v>
+        <v>43.738</v>
       </c>
       <c r="E21">
-        <v>44.197000000000003</v>
+        <v>43.911000000000001</v>
       </c>
       <c r="F21">
-        <v>45.345999999999997</v>
+        <v>45.139000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
@@ -871,99 +871,99 @@
         <v>2008</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>43.514000000000003</v>
+        <v>42.95</v>
       </c>
       <c r="D22">
-        <v>43.91</v>
+        <v>43.540999999999997</v>
       </c>
       <c r="E22">
-        <v>43.957999999999998</v>
+        <v>44.197000000000003</v>
       </c>
       <c r="F22">
-        <v>45.030999999999999</v>
+        <v>45.345999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23">
-        <v>43.917000000000002</v>
+        <v>43.514000000000003</v>
       </c>
       <c r="D23">
-        <v>44.036000000000001</v>
+        <v>43.91</v>
       </c>
       <c r="E23">
-        <v>44.137999999999998</v>
+        <v>43.957999999999998</v>
       </c>
       <c r="F23">
-        <v>45.487000000000002</v>
+        <v>45.030999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>44.194000000000003</v>
+        <v>43.917000000000002</v>
       </c>
       <c r="D24">
-        <v>44.406999999999996</v>
+        <v>44.036000000000001</v>
       </c>
       <c r="E24">
-        <v>44.591000000000001</v>
+        <v>44.137999999999998</v>
       </c>
       <c r="F24">
-        <v>45.707999999999998</v>
+        <v>45.487000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
       </c>
       <c r="C25">
-        <v>44.337000000000003</v>
+        <v>44.194000000000003</v>
       </c>
       <c r="D25">
-        <v>44.575000000000003</v>
+        <v>44.406999999999996</v>
       </c>
       <c r="E25">
-        <v>44.631999999999998</v>
+        <v>44.591000000000001</v>
       </c>
       <c r="F25">
-        <v>46.597000000000001</v>
+        <v>45.707999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
       </c>
       <c r="C26">
-        <v>44.421999999999997</v>
+        <v>44.337000000000003</v>
       </c>
       <c r="D26">
-        <v>44.481999999999999</v>
+        <v>44.575000000000003</v>
       </c>
       <c r="E26">
-        <v>44.844999999999999</v>
+        <v>44.631999999999998</v>
       </c>
       <c r="F26">
-        <v>45.31</v>
+        <v>46.597000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
@@ -971,58 +971,78 @@
         <v>2004</v>
       </c>
       <c r="B27" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>44.179000000000002</v>
+        <v>44.421999999999997</v>
       </c>
       <c r="D27">
-        <v>44.250999999999998</v>
+        <v>44.481999999999999</v>
       </c>
       <c r="E27">
-        <v>44.354999999999997</v>
+        <v>44.844999999999999</v>
       </c>
       <c r="F27">
-        <v>44.985999999999997</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>44.813000000000002</v>
+        <v>44.179000000000002</v>
       </c>
       <c r="D28">
-        <v>44.890999999999998</v>
+        <v>44.250999999999998</v>
       </c>
       <c r="E28">
-        <v>44.957999999999998</v>
+        <v>44.354999999999997</v>
       </c>
       <c r="F28">
-        <v>45.982999999999997</v>
+        <v>44.985999999999997</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
+        <v>2002</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>44.813000000000002</v>
+      </c>
+      <c r="D29">
+        <v>44.890999999999998</v>
+      </c>
+      <c r="E29">
+        <v>44.957999999999998</v>
+      </c>
+      <c r="F29">
+        <v>45.982999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30">
         <v>2000</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>2</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>44.424999999999997</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>44.658999999999999</v>
       </c>
-      <c r="E29">
+      <c r="E30">
         <v>44.719000000000001</v>
       </c>
-      <c r="F29">
+      <c r="F30">
         <v>45.701000000000001</v>
       </c>
     </row>

--- a/pages/WR_progressions/Medals_Men_TS.xlsx
+++ b/pages/WR_progressions/Medals_Men_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E039E70-9AE9-45E1-B1A4-0B703C96B76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B12809-5002-4042-A7C9-FD5E66615EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>

--- a/pages/WR_progressions/Medals_Men_TS.xlsx
+++ b/pages/WR_progressions/Medals_Men_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B12809-5002-4042-A7C9-FD5E66615EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9760257F-6DC0-49E4-826F-02E54A7BA410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="5" max="5" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,327 +463,331 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>42.588999999999999</v>
-      </c>
-      <c r="D2">
-        <v>42.993000000000002</v>
-      </c>
-      <c r="E2">
-        <v>42.997999999999998</v>
+      <c r="C2" s="1">
+        <v>41.86</v>
+      </c>
+      <c r="D2" s="1">
+        <v>42.131</v>
+      </c>
+      <c r="E2" s="1">
+        <v>42.691000000000003</v>
       </c>
       <c r="F2" s="1">
-        <v>44.186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>43.234000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2024</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>42.588999999999999</v>
+      </c>
+      <c r="D3">
+        <v>42.993000000000002</v>
+      </c>
+      <c r="E3">
+        <v>42.997999999999998</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44.186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C4" s="1">
         <v>41.279000000000003</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D4" s="1">
         <v>41.862000000000002</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E4" s="1">
         <v>42.072000000000003</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F4" s="1">
         <v>43.905000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5">
         <v>2023</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
         <v>42.045999999999999</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>42.530999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>42.915999999999997</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>43.658000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6">
         <v>2022</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <v>41.896000000000001</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>41.993000000000002</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>42.851999999999997</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>43.707000000000001</v>
       </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>42.69</v>
-      </c>
-      <c r="D6">
-        <v>42.965000000000003</v>
-      </c>
-      <c r="E6">
-        <v>43.250999999999998</v>
-      </c>
-      <c r="F6">
-        <v>44.414000000000001</v>
-      </c>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2021</v>
       </c>
       <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>42.69</v>
+      </c>
+      <c r="D7">
+        <v>42.965000000000003</v>
+      </c>
+      <c r="E7">
+        <v>43.250999999999998</v>
+      </c>
+      <c r="F7">
+        <v>44.414000000000001</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>42.134</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>42.231000000000002</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>42.371000000000002</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>43.515999999999998</v>
       </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9">
         <v>2020</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
         <v>41.987000000000002</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>42.470999999999997</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>42.805</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>43.235999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2019</v>
       </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
         <v>42.573999999999998</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>43.357999999999997</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>43.387999999999998</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>43.704000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11">
         <v>2018</v>
       </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
         <v>42.869</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>43.389000000000003</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>43.451999999999998</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>44.41</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12">
         <v>2017</v>
       </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11">
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>43.267000000000003</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>43.39</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>43.415999999999997</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>44.363</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>2016</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>42.561999999999998</v>
-      </c>
-      <c r="D12">
-        <v>42.673000000000002</v>
-      </c>
-      <c r="E12">
-        <v>43.158000000000001</v>
-      </c>
-      <c r="F12">
-        <v>44.262999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2016</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
+        <v>42.561999999999998</v>
+      </c>
+      <c r="D13">
+        <v>42.673000000000002</v>
+      </c>
+      <c r="E13">
+        <v>43.158000000000001</v>
+      </c>
+      <c r="F13">
+        <v>44.262999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2016</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
         <v>43.095999999999997</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>43.265999999999998</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>43.487000000000002</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>43.750999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>2015</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
         <v>42.892000000000003</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>43.072000000000003</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>43.136000000000003</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>43.808</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16">
         <v>2014</v>
       </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15">
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
         <v>43.064999999999998</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>43.301000000000002</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>43.454000000000001</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <v>43.924999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>2013</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>43.58</v>
-      </c>
-      <c r="D16">
-        <v>43.731000000000002</v>
-      </c>
-      <c r="E16">
-        <v>43.792000000000002</v>
-      </c>
-      <c r="F16">
-        <v>44.854999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>43.247</v>
+        <v>43.58</v>
       </c>
       <c r="D17">
-        <v>43.512</v>
+        <v>43.731000000000002</v>
       </c>
       <c r="E17">
-        <v>43.741999999999997</v>
+        <v>43.792000000000002</v>
       </c>
       <c r="F17">
-        <v>44.399000000000001</v>
+        <v>44.854999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
@@ -791,99 +795,99 @@
         <v>2012</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>43.064999999999998</v>
+        <v>43.247</v>
       </c>
       <c r="D18">
-        <v>43.097000000000001</v>
+        <v>43.512</v>
       </c>
       <c r="E18">
-        <v>43.377000000000002</v>
+        <v>43.741999999999997</v>
       </c>
       <c r="F18">
-        <v>44.323999999999998</v>
+        <v>44.399000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>43.951000000000001</v>
+        <v>43.064999999999998</v>
       </c>
       <c r="D19">
-        <v>44.100999999999999</v>
+        <v>43.097000000000001</v>
       </c>
       <c r="E19">
-        <v>44.128</v>
+        <v>43.377000000000002</v>
       </c>
       <c r="F19">
-        <v>45.112000000000002</v>
+        <v>44.323999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>43.372999999999998</v>
+        <v>43.951000000000001</v>
       </c>
       <c r="D20">
-        <v>43.457999999999998</v>
+        <v>44.100999999999999</v>
       </c>
       <c r="E20">
-        <v>43.802</v>
+        <v>44.128</v>
       </c>
       <c r="F20">
-        <v>44.63</v>
+        <v>45.112000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21">
-        <v>43.613999999999997</v>
+        <v>43.372999999999998</v>
       </c>
       <c r="D21">
-        <v>43.738</v>
+        <v>43.457999999999998</v>
       </c>
       <c r="E21">
-        <v>43.911000000000001</v>
+        <v>43.802</v>
       </c>
       <c r="F21">
-        <v>45.139000000000003</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B22" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>42.95</v>
+        <v>43.613999999999997</v>
       </c>
       <c r="D22">
-        <v>43.540999999999997</v>
+        <v>43.738</v>
       </c>
       <c r="E22">
-        <v>44.197000000000003</v>
+        <v>43.911000000000001</v>
       </c>
       <c r="F22">
-        <v>45.345999999999997</v>
+        <v>45.139000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
@@ -891,99 +895,99 @@
         <v>2008</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>43.514000000000003</v>
+        <v>42.95</v>
       </c>
       <c r="D23">
-        <v>43.91</v>
+        <v>43.540999999999997</v>
       </c>
       <c r="E23">
-        <v>43.957999999999998</v>
+        <v>44.197000000000003</v>
       </c>
       <c r="F23">
-        <v>45.030999999999999</v>
+        <v>45.345999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>43.917000000000002</v>
+        <v>43.514000000000003</v>
       </c>
       <c r="D24">
-        <v>44.036000000000001</v>
+        <v>43.91</v>
       </c>
       <c r="E24">
-        <v>44.137999999999998</v>
+        <v>43.957999999999998</v>
       </c>
       <c r="F24">
-        <v>45.487000000000002</v>
+        <v>45.030999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
       </c>
       <c r="C25">
-        <v>44.194000000000003</v>
+        <v>43.917000000000002</v>
       </c>
       <c r="D25">
-        <v>44.406999999999996</v>
+        <v>44.036000000000001</v>
       </c>
       <c r="E25">
-        <v>44.591000000000001</v>
+        <v>44.137999999999998</v>
       </c>
       <c r="F25">
-        <v>45.707999999999998</v>
+        <v>45.487000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
       </c>
       <c r="C26">
-        <v>44.337000000000003</v>
+        <v>44.194000000000003</v>
       </c>
       <c r="D26">
-        <v>44.575000000000003</v>
+        <v>44.406999999999996</v>
       </c>
       <c r="E26">
-        <v>44.631999999999998</v>
+        <v>44.591000000000001</v>
       </c>
       <c r="F26">
-        <v>46.597000000000001</v>
+        <v>45.707999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>44.421999999999997</v>
+        <v>44.337000000000003</v>
       </c>
       <c r="D27">
-        <v>44.481999999999999</v>
+        <v>44.575000000000003</v>
       </c>
       <c r="E27">
-        <v>44.844999999999999</v>
+        <v>44.631999999999998</v>
       </c>
       <c r="F27">
-        <v>45.31</v>
+        <v>46.597000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
@@ -991,58 +995,78 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>44.179000000000002</v>
+        <v>44.421999999999997</v>
       </c>
       <c r="D28">
-        <v>44.250999999999998</v>
+        <v>44.481999999999999</v>
       </c>
       <c r="E28">
-        <v>44.354999999999997</v>
+        <v>44.844999999999999</v>
       </c>
       <c r="F28">
-        <v>44.985999999999997</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>44.813000000000002</v>
+        <v>44.179000000000002</v>
       </c>
       <c r="D29">
-        <v>44.890999999999998</v>
+        <v>44.250999999999998</v>
       </c>
       <c r="E29">
-        <v>44.957999999999998</v>
+        <v>44.354999999999997</v>
       </c>
       <c r="F29">
-        <v>45.982999999999997</v>
+        <v>44.985999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30">
+        <v>2002</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>44.813000000000002</v>
+      </c>
+      <c r="D30">
+        <v>44.890999999999998</v>
+      </c>
+      <c r="E30">
+        <v>44.957999999999998</v>
+      </c>
+      <c r="F30">
+        <v>45.982999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31">
         <v>2000</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>2</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>44.424999999999997</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>44.658999999999999</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>44.719000000000001</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>45.701000000000001</v>
       </c>
     </row>
